--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -598,122 +598,84 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Test script</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Each workpaper has a 'New Test Script' tab answering the 9 steps of the IT RCSA 2026 Test Plan NewTest Script (C13, C25 verbatim; no script exists for C1 – same 9-step structure applied). Test plan copy: 00 Reference/IT_RCSA_2026_Test_Plan-Test.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Control ID</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Control Name</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Evidence provided?</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Tested?</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Samples (projects / releases)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Exceptions</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Open items</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>CDA rating</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>CPA rating</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Workpaper</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>BSI.IT.23.C1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Business Requirement</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Yes – BRDs, sponsor approvals (both projects); Gate 4 records (NDF only)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2 / 4</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>OI-01</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Satisfactory</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pending – OI-01 (preliminary Satisfactory for NDF)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>BSI.IT.23.C1 Business Requirement/WP 2026 BSI.IT.23.C1 Business Requirement.xlsm</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13</t>
+          <t>BSI.IT.23.C1</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Design of System</t>
+          <t>Business Requirement</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Partial – Data Risk Assessments only; no Enterprise Architecture evidence</t>
+          <t>Yes – BRDs, sponsor approvals (both projects); Gate 4 records (NDF only)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -731,7 +693,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>OI-02</t>
+          <t>OI-01, OI-03</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -741,277 +703,275 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
+          <t>Pending – OI-01 (preliminary Satisfactory for NDF)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C1 Business Requirement/WP 2026 BSI.IT.23.C1 Business Requirement.xlsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C13</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Design of System</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Partial – Data Risk Assessments only; no Enterprise Architecture evidence</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2 / 4</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>OI-02, OI-03</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
           <t>Pending – OI-02 (unable to conclude)</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>BSI.IT.23.C13 Design of System/WP 2026 BSI.IT.23.C13 Design of System.xlsm</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>BSI.IT.23.C25</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Implement &amp; Deployment</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Yes – release tickets, PIPs / deployment plan (all 4 releases)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>2 / 4</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>OI-03</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Satisfactory</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Satisfactory – subject to OI-03</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>BSI.IT.23.C25 Implement &amp; Deployment/WP 2026 BSI.IT.23.C25 Implement &amp; Deployment.xlsm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>BSI.IT.23.C4</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Segregated Environments</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>No – evidence folders empty for both projects</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Segregated Environments</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>No – evidence folders empty for both projects</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>BSI.IT.23.C17</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Solution Intent Document</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>No – evidence folders empty for both projects</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Sample results by release</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Release / Change</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Prod date</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>C1 BRD defined</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>C1 BRD approved before Build</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>C13 Architecture approved</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>C13 DRA approved by CDO</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>C25 Plan documented</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>C25 Plan approved before prod</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>3263 ALCO – Security Lending</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>R01 (Appian SLW)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>RLSE1271544 / CHG002674318</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Pending – OI-01</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Pending – OI-02</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1023,17 +983,17 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>R02 (T24)</t>
+          <t>R01 (Appian SLW)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>RLSE1370716 / CHG003017994</t>
+          <t>RLSE1271544 / CHG002674318</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>06/26/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1043,7 +1003,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Pass (Gate 4 record pending – OI-01)</t>
+          <t>Pending – OI-01</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1070,22 +1030,22 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>3264 NDF</t>
+          <t>3263 ALCO – Security Lending</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02 (T24)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>RLSE1270306 / CHG002670462</t>
+          <t>RLSE1370716 / CHG003017994</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>01/28/2026</t>
+          <t>06/26/2026</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1093,19 +1053,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Pass (Gate 4 record pending – OI-01)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Pending – OI-02</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Pending – OI-02</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Pass (date pending)</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -1127,52 +1087,105 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>RLSE1270306 / CHG002670462</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>01/28/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Pending – OI-02</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Pass (date pending)</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>3264 NDF</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>RLSE1329424 / CHG002864467</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>05/08/2026</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Pending – OI-02</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Pass (date pending)</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B9:I9"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B5:I5"/>
@@ -1180,9 +1193,9 @@
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2524,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2662,37 +2675,37 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>OBS-01</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>2026 SDLC process map (v2.0) is still in Draft – Date Approved / Approved By blank.</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Approved 2026 process map.</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Observation only.</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>OI-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>C1, C13, C25</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Population (SDLC Project List)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>NewTest Script step 2 (completeness &amp; accuracy): accuracy of the 2 in-scope projects traced to ServiceNow releases; no independent release list provided for completeness. Projects 3512 Discretionary Portfolio Mandate (Closed 03/30/2026) and 3625 Alternative Investments 2025 (Closed) are Technology (IT Change) projects with a blank SDLC flag and no documented classification.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ServiceNow production release list (RLSE, category Deployment) for 09/01/2025 – 08/31/2026; PMO rationale for SDLC classification of 3512 and 3625.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>If 3512 / 3625 involved development, add them to the population and test them for C1, C13 and C25.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2701,27 +2714,27 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>OBS-02</t>
+          <t>OBS-01</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>3263 Security Lending</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>BRDs only populate the Security non-functional section (others 'NA'); R02 BRD revision history ends at v0.2 although approved.</t>
+          <t>2026 SDLC process map (v2.0) is still in Draft – Date Approved / Approved By blank.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>N/A – recommendation to complete NFR sections and versioning per US PMO template.</t>
+          <t>Approved 2026 process map.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -2738,35 +2751,72 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>OBS-02</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C1</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>3263 Security Lending</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>BRDs only populate the Security non-functional section (others 'NA'); R02 BRD revision history ends at v0.2 although approved.</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>N/A – recommendation to complete NFR sections and versioning per US PMO template.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
           <t>OBS-03</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>BSI.IT.23.C25</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>3263 R01 / 3264 R02</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>RLSE1271544 Deployment Plan roll-back rows left blank (rollback in ticket). RLSE1329424 final PIP v1.3 attached after CHG approvals (before implementation).</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Observation only – no impact on conclusion.</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Open</t>
         </is>

--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Each workpaper has a 'New Test Script' tab answering the 9 steps of the IT RCSA 2026 Test Plan NewTest Script (C13, C25 verbatim; no script exists for C1 – same 9-step structure applied). Test plan copy: 00 Reference/IT_RCSA_2026_Test_Plan-Test.xlsx.</t>
+          <t>Each workpaper has a 'New Test Script' tab answering the 9 steps of the IT RCSA 2026 Test Plan NewTest Script (C13, C25 verbatim from the plan; C1 has no script in the plan – proposed C1 script drafted in the same format: 00 Reference/BSI.IT.23.C1 NewTest Script (proposed).xlsx). Test plan copy: 00 Reference/IT_RCSA_2026_Test_Plan-Test.xlsx.</t>
         </is>
       </c>
     </row>

--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -610,6 +610,18 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Testing Procedures</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Testing Procedures: each control folder holds a BSI.IT.23.Cx_..._Testing_Procedures.docx in the format of the C25 Testing Procedures provided (no tables).</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -799,7 +811,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>OI-03</t>
+          <t>OI-03, OI-06</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -809,7 +821,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Satisfactory – subject to OI-03</t>
+          <t>Satisfactory (preliminary) – subject to OI-03, OI-06</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -3886,7 +3898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4137,32 +4149,32 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>OBS-01</t>
+          <t>OI-06</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSI.IT.23.C25</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All 4 releases</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026 SDLC process map (v2.0) is still in Draft – Date Approved / Approved By blank.</t>
+          <t>Final implementation plan attached after the last approval in all four releases; earlier versions deleted, so the approved and deployed versions cannot be matched (SL R01 plan at approval time named "Cornercard").</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Approved 2026 process map.</t>
+          <t>Control owner confirmation that revisions were non-substantive (or earlier versions) and whether Change Management requires re-approval of revised plans.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Observation only.</t>
+          <t>C25 CPA preliminary until confirmed.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -4174,27 +4186,27 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>OBS-02</t>
+          <t>OBS-01</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>3263 Security Lending</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>BRDs only populate the Security non-functional section (others 'NA'); R02 BRD revision history ends at v0.2.</t>
+          <t>2026 SDLC process map (v2.0) is still in Draft – Date Approved / Approved By blank.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>N/A – recommendation.</t>
+          <t>Approved 2026 process map.</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -4211,27 +4223,27 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>OBS-03</t>
+          <t>OBS-02</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25</t>
+          <t>BSI.IT.23.C1</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>3263 R01 / 3264 R02</t>
+          <t>3263 Security Lending</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>RLSE1271544 Deployment Plan roll-back rows blank (rollback in ticket). RLSE1329424 final PIP v1.3 attached after CHG approvals (before implementation).</t>
+          <t>BRDs only populate the Security non-functional section (others 'NA'); R02 BRD revision history ends at v0.2.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A – recommendation.</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -4248,32 +4260,32 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>OBS-04</t>
+          <t>OBS-03</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>C13, C17</t>
+          <t>BSI.IT.23.C25</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>All releases</t>
+          <t>3263 R01 / 3264 R02</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>EA approval / ARB determination obtained as Gate 5 artifacts, after the Gate 4 (PTB) start of Build. Statement does not define timing; 2026 proposed statements require approval before development.</t>
+          <t>RLSE1271544 Deployment Plan roll-back rows blank (rollback in ticket). RLSE1329424 final PIP v1.3 attached after CHG approvals (before implementation).</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Make the EA / ARB determination a PTB prerequisite.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Observation – would be an exception if ARB were required.</t>
+          <t>Observation only.</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -4285,32 +4297,32 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>OBS-05</t>
+          <t>OBS-04</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13</t>
+          <t>C13, C17</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>3264 NDF</t>
+          <t>All releases</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>DRA HIGH – CDO-mandated data model / lineage deliverables not provided separately; reliance on CDO gate approval and EA-approved Data Flow Guide.</t>
+          <t>EA approval / ARB determination obtained as Gate 5 artifacts, after the Gate 4 (PTB) start of Build. Statement does not define timing; 2026 proposed statements require approval before development.</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Store CDO deliverables with the DRA in Delivery Hub.</t>
+          <t>Make the EA / ARB determination a PTB prerequisite.</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Observation only.</t>
+          <t>Observation – would be an exception if ARB were required.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -4322,27 +4334,27 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>OBS-06</t>
+          <t>OBS-05</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1</t>
+          <t>BSI.IT.23.C13</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3264 NDF</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Control statement lacks who / evidence / handling of requirement changes (Test Plan Control Articulation Tracker).</t>
+          <t>DRA HIGH – CDO-mandated data model / lineage deliverables not provided separately; reliance on CDO gate approval and EA-approved Data Flow Guide.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Adopt 2026 proposed statement (PM obtains sponsor e-mail approval; changes escalated for documented amendment).</t>
+          <t>Store CDO deliverables with the DRA in Delivery Hub.</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -4359,12 +4371,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>OBS-07</t>
+          <t>OBS-06</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17</t>
+          <t>BSI.IT.23.C1</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -4374,12 +4386,12 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>C17 present in the 2025 process map (step 1.3) but not in the 2026 map v2.0, although an active Key Control.</t>
+          <t>Control statement lacks who / evidence / handling of requirement changes (Test Plan Control Articulation Tracker).</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Add C17 to the 2026 map.</t>
+          <t>Adopt 2026 proposed statement (PM obtains sponsor e-mail approval; changes escalated for documented amendment).</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -4396,7 +4408,7 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>OBS-08</t>
+          <t>OBS-07</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -4406,17 +4418,17 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>3263 Security Lending</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Single Design shows DH ID 1886 / "Securities Lending (JP Morgan)", undated version rows; approved attachments not retained in the .msg; decks re-saved 10/28/2026.</t>
+          <t>C17 present in the 2025 process map (step 1.3) but not in the 2026 map v2.0, although an active Key Control.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Keep approved version (PDF) with the approval in Delivery Hub.</t>
+          <t>Add C17 to the 2026 map.</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -4433,48 +4445,122 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>OBS-08</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C17</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>3263 Security Lending</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Single Design shows DH ID 1886 / "Securities Lending (JP Morgan)", undated version rows; approved attachments not retained in the .msg; decks re-saved 10/28/2026.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Keep approved version (PDF) with the approval in Delivery Hub.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>OBS-09</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>BSI.IT.23.C4</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Statement lacks who / when / evidence; exception process only partially defined; Heracles frequency Annual vs per-release activity.</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Adopt 2026 proposed statement (CISO approval; evidence of domains, repositories, hosts).</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Observation only.</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>OBS-10</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C25</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>All 4 releases</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Implementation plan versions are deleted and re-attached in ServiceNow, so the approved version is not retained.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Retain the approved version (version control).</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>100% of population (2 projects / 4 releases) for the 'In every operation' controls; C4 is Annual – 1 occurrence (T24 environments).</t>
+          <t>100% of population (2 projects / 4 releases) for the 'In every operation' controls; the samples for every control are the 2 projects provided in the evidence folder (ALCO – Security Lending, Derivatives NDF).</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>1 (annual)</t>
+          <t>2 / 4</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Pass (DEV + UAT); Appian env. pending OI-04</t>
+          <t>Pass T24 (DEV + UAT); Appian env. pending OI-04</t>
         </is>
       </c>
     </row>

--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -1225,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/00 Common - process map and population/BSI.IT.23.C1.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.02 - SDLC Project List (population).xlsx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/00 Common - process map and population/BSI.IT.23.C1.02 - SDLC Project List (population).xlsx</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.03 - Security Lending R01 - 3263 SECLENDING Business Requirements Document FINAL.docx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.03 - Security Lending R01 - 3263 SECLENDING Business Requirements Document FINAL.docx</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.04 - Security Lending R01 - Sponsor Approval email 02-06-2026 (extracted from C1.03).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.04 - Security Lending R01 - Sponsor Approval email 02-06-2026 (extracted from C1.03).msg</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.05 - Security Lending R02 - 3263 Business Requirements FINAL.docx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.05 - Security Lending R02 - 3263 Business Requirements FINAL.docx</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.06 - Security Lending R02 - Sponsor Approval email 04-29-2026 (extracted from C1.05).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.06 - Security Lending R02 - Sponsor Approval email 04-29-2026 (extracted from C1.05).msg</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.07 - NDF R01 - DH 3264 Business Requirements Document_final.docx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.07 - NDF R01 - DH 3264 Business Requirements Document_final.docx</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.08 - NDF R01 - BRD Sponsor Sign-off email 10-23-2025 (extracted from C1.07).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.08 - NDF R01 - BRD Sponsor Sign-off email 10-23-2025 (extracted from C1.07).msg</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.09 - NDF R01 - Delivery Hub Gate 4 (PTB) approval 11-04-2025.pdf</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.09 - NDF R01 - Delivery Hub Gate 4 (PTB) approval 11-04-2025.pdf</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.10 - NDF R02 - DH 3264 RL2 Business Requirements Document_final.docx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.10 - NDF R02 - DH 3264 RL2 Business Requirements Document_final.docx</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.11 - NDF R02 - BRD Sponsor Sign-off email 12-02-2025 (extracted from C1.10).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.11 - NDF R02 - BRD Sponsor Sign-off email 12-02-2025 (extracted from C1.10).msg</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.12 - NDF R02 - Delivery Hub Gate 4 (PTB) approval 03-10-2026.pdf</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C1.12 - NDF R02 - Delivery Hub Gate 4 (PTB) approval 03-10-2026.pdf</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.13 - Security Lending - Delivery Hub Gate dispositions (PTP 08-01-2025, PTB 10-31-2025 ALL) (cross-ref C13.05).docx</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.13 - Security Lending - Delivery Hub Gate dispositions (PTP 08-01-2025, PTB 10-31-2025 ALL) (cross-ref C13.05).docx</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.14 - Security Lending - Appian release 2 rationale email chain 02-03 to 02-09-2026 (cross-ref C13.08).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.14 - Security Lending - Appian release 2 rationale email chain 02-03 to 02-09-2026 (cross-ref C13.08).msg</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C1 Business Requirement/Evidence/BSI.IT.23.C1.15 - Security Lending - T24 last release email chain 05-04 to 05-12-2026, Gate 4 on 05-15-2026 (cross-ref C13.09).msg</t>
+          <t>BSI.IT.23.C1 Business Requirement/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C1.15 - Security Lending - T24 last release email chain 05-04 to 05-12-2026, Gate 4 on 05-15-2026 (cross-ref C13.09).msg</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/00 Common - process map and population/BSI.IT.23.C13.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.02 - SDLC Project List (population).xlsx</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/00 Common - process map and population/BSI.IT.23.C13.02 - SDLC Project List (population).xlsx</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.03 - Security Lending - Data Risk Assessment (CDO Approved, Low).pdf</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C13.03 - Security Lending - Data Risk Assessment (CDO Approved, Low).pdf</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.04 - NDF - Data Risk Assessment (CDO Approved, High).pdf</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C13.04 - NDF - Data Risk Assessment (CDO Approved, High).pdf</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.05 - Security Lending - DRA Approval and Gate 3 (PTP) disposition 10-01-2025 (CDO Out, DRA Low).docx</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C13.05 - Security Lending - DRA Approval and Gate 3 (PTP) disposition 10-01-2025 (CDO Out, DRA Low).docx</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.06 - NDF - DRA Approval and Gate 3 (PTP) disposition 07-28-2025 (CDO In, DRA High).docx</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C13.06 - NDF - DRA Approval and Gate 3 (PTP) disposition 07-28-2025 (CDO In, DRA High).docx</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.07 - Security Lending - Enterprise Architecture approval email 12-04-2025 (extracted from C17 Single Design).msg</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C13.07 - Security Lending - Enterprise Architecture approval email 12-04-2025 (extracted from C17 Single Design).msg</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.08 - Security Lending - EA confirmation Appian release no architecture impact 02-09-2026 (extracted).msg</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C13.08 - Security Lending - EA confirmation Appian release no architecture impact 02-09-2026 (extracted).msg</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.09 - Security Lending - EA confirmation T24 release no ARB required 05-12-2026 (extracted).msg</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C13.09 - Security Lending - EA confirmation T24 release no ARB required 05-12-2026 (extracted).msg</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.10 - NDF R01 - Single Technical Design sign-off Enterprise Architecture 12-10-2025.msg</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C13.10 - NDF R01 - Single Technical Design sign-off Enterprise Architecture 12-10-2025.msg</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C13 Design of System/Evidence/BSI.IT.23.C13.11 - NDF R02 - Single Technical Design sign-off Enterprise Architecture 03-24-2026.msg</t>
+          <t>BSI.IT.23.C13 Design of System/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C13.11 - NDF R02 - Single Technical Design sign-off Enterprise Architecture 03-24-2026.msg</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/00 Common - process map and population/BSI.IT.23.C25.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.02 - SDLC Project List (population).xlsx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/00 Common - process map and population/BSI.IT.23.C25.02 - SDLC Project List (population).xlsx</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.03 - Security Lending R01 - RLSE1271544 ServiceNow Release ticket.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C25.03 - Security Lending R01 - RLSE1271544 ServiceNow Release ticket.pdf</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.04 - Security Lending R01 - Deployment Plan FINAL.xlsx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C25.04 - Security Lending R01 - Deployment Plan FINAL.xlsx</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.05 - Security Lending R01 - Workflow Functional doc.docx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C25.05 - Security Lending R01 - Workflow Functional doc.docx</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.06 - Security Lending R02 - RLSE1370716 ServiceNow Release ticket.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C25.06 - Security Lending R02 - RLSE1370716 ServiceNow Release ticket.pdf</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.07 - Security Lending R02 - PIP-RLSE1370716 Implementation Plan.docx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C25.07 - Security Lending R02 - PIP-RLSE1370716 Implementation Plan.docx</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.08 - NDF R01 - RLSE1270306 ServiceNow Release ticket.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.08 - NDF R01 - RLSE1270306 ServiceNow Release ticket.pdf</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.09 - NDF R01 - RLSE1270306 ServiceNow screenshot.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.09 - NDF R01 - RLSE1270306 ServiceNow screenshot.pdf</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.10 - NDF R01 - PIP ND Deal Implementation Plan.docx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.10 - NDF R01 - PIP ND Deal Implementation Plan.docx</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.11 - NDF R02 - RLSE1329424 ServiceNow Release ticket.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.11 - NDF R02 - RLSE1329424 ServiceNow Release ticket.pdf</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.12 - NDF R02 - RLSE1329424 ServiceNow screenshot.pdf</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.12 - NDF R02 - RLSE1329424 ServiceNow screenshot.pdf</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/BSI.IT.23.C25.13 - NDF R02 - PIP ND Deal Release2 v1.3 Implementation Plan.docx</t>
+          <t>BSI.IT.23.C25 Implement &amp; Deployment/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C25.13 - NDF R02 - PIP ND Deal Release2 v1.3 Implementation Plan.docx</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.01 - 2025 PM_Systems Development Life Cycle (BSI)_v1 (C17 at step 1.3).pdf</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/00 Common - process map and population/BSI.IT.23.C17.01 - 2025 PM_Systems Development Life Cycle (BSI)_v1 (C17 at step 1.3).pdf</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.02 - 2026 PM_Systems Development Life Cycle (BSI)_v1 (C17 not listed).pdf</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/00 Common - process map and population/BSI.IT.23.C17.02 - 2026 PM_Systems Development Life Cycle (BSI)_v1 (C17 not listed).pdf</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.03 - SDLC Project List (population).xlsx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/00 Common - process map and population/BSI.IT.23.C17.03 - SDLC Project List (population).xlsx</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.04 - Security Lending - Single Design FINAL (Feb 2026, R01 Appian) with embedded EA approvals.pptx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.04 - Security Lending - Single Design FINAL (Feb 2026, R01 Appian) with embedded EA approvals.pptx</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.05 - Security Lending - IT Architecture (EA) approval email 12-04-2025 (extracted from C17.04).msg</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.05 - Security Lending - IT Architecture (EA) approval email 12-04-2025 (extracted from C17.04).msg</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.06 - Security Lending - EA confirmation Appian release no architecture impact 02-09-2026 (extracted from C17.04).msg</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.06 - Security Lending - EA confirmation Appian release no architecture impact 02-09-2026 (extracted from C17.04).msg</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.07 - Security Lending - Single Design FINAL (May 2026, R02 T24) with embedded EA confirmation.pptx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.07 - Security Lending - Single Design FINAL (May 2026, R02 T24) with embedded EA confirmation.pptx</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.08 - Security Lending - EA confirmation R02 no ARB required 05-12-2026 (extracted from C17.07).msg</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.08 - Security Lending - EA confirmation R02 no ARB required 05-12-2026 (extracted from C17.07).msg</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.09 - NDF R01 - Single Technical Design final (12-08-2025).pptx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C17.09 - NDF R01 - Single Technical Design final (12-08-2025).pptx</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.10 - NDF R01 - Single Technical Design sign-off Enterprise Architecture 12-10-2025.msg</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C17.10 - NDF R01 - Single Technical Design sign-off Enterprise Architecture 12-10-2025.msg</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.11 - NDF R02 - Single Technical Design final (03-20-2026).pptx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C17.11 - NDF R02 - Single Technical Design final (03-20-2026).pptx</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.12 - NDF R02 - Single Technical Design sign-off Enterprise Architecture 03-24-2026.msg</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C17.12 - NDF R02 - Single Technical Design sign-off Enterprise Architecture 03-24-2026.msg</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.13 - Security Lending - Delivery Hub Gate dispositions (cross-ref C13.05).docx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C17.13 - Security Lending - Delivery Hub Gate dispositions (cross-ref C13.05).docx</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/BSI.IT.23.C17.14 - NDF - Delivery Hub Gate dispositions (cross-ref C13.06).docx</t>
+          <t>BSI.IT.23.C17 Solution Intent Document/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C17.14 - NDF - Delivery Hub Gate dispositions (cross-ref C13.06).docx</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/00 Common - process map and population/BSI.IT.23.C4.01 - 2026 PM_Systems Development Life Cycle (BSI)_v1.pdf</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.02 - SDLC Project List (population).xlsx</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/00 Common - process map and population/BSI.IT.23.C4.02 - SDLC Project List (population).xlsx</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.03 - Segregated Environments - T24 production vs non-production (server, IP, environment, ND.DEAL).docx</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C4.03 - Security Lending - Segregated Environments - T24 production vs non-production (server, IP, environment, ND.DEAL).docx</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.04 - NDF R01 - RLSE1270306 ServiceNow Release ticket (SIT-UAT in test, cross-ref C25.08).pdf</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C4.04 - NDF R01 - RLSE1270306 ServiceNow Release ticket (SIT-UAT in test, cross-ref C25.08).pdf</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.05 - NDF R02 - RLSE1329424 ServiceNow Release ticket (cross-ref C25.11).pdf</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C4.05 - NDF R02 - RLSE1329424 ServiceNow Release ticket (cross-ref C25.11).pdf</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.06 - Security Lending R01 - RLSE1271544 ServiceNow Release ticket (DEV unit test, UAT, cross-ref C25.03).pdf</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C4.06 - Security Lending R01 - RLSE1271544 ServiceNow Release ticket (DEV unit test, UAT, cross-ref C25.03).pdf</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>BSI.IT.23.C4 Segregated Environments/Evidence/BSI.IT.23.C4.07 - Security Lending R02 - RLSE1370716 ServiceNow Release ticket (SIT-UAT, cross-ref C25.06).pdf</t>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 1 - ALCO - Security Lending/BSI.IT.23.C4.07 - Security Lending R02 - RLSE1370716 ServiceNow Release ticket (SIT-UAT, cross-ref C25.06).pdf</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -3815,14 +3815,56 @@
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="12" t="n"/>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="13" t="n"/>
-      <c r="H65" s="12" t="n"/>
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4.08</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>NDF (3264)</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>T24 production vs non-production – environment evidence from the NDF folder (identical file to C4.03)</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Sample 2 – Attr 1</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4 Segregated Environments/Evidence/Sample 2 - Derivatives Non-Deliverable Forwards (NDF)/BSI.IT.23.C4.08 - NDF - Segregated Environments - T24 production vs non-production (server, IP, environment, ND.DEAL).docx</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>Evidence/&lt;both projects&gt;/BSI.IT.23.C4 – Segregated Environments/BSI.IT.23.C4 – Segregated Environments.docx (identical file in both project folders)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="12" t="n"/>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="n"/>
+      <c r="G66" s="13" t="n"/>
+      <c r="H66" s="12" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H33"/>
@@ -3887,6 +3929,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 SDLC 2026 Testing Summary & Evidence Index.xlsx
@@ -613,12 +613,12 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Testing Procedures</t>
+          <t>Testing Procedures / Audit Workpapers</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Testing Procedures: each control folder holds a BSI.IT.23.Cx_..._Testing_Procedures.docx in the format of the C25 Testing Procedures provided (no tables).</t>
+          <t>Each control folder holds a Testing Procedures document (C25 format, no tables) and an IT Audit Workpaper – Sample Size of 1 (BSI.IT.23.Cx_Audit_Workpaper_Sample_Size_1.docx) answering every test step for each of the two samples with inline evidence references.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>OI-01, OI-03</t>
+          <t>EX-C1-01; OBS-11</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Needs Improvement (proposed) – pending CO / BCO agreement</t>
+          <t>Needs Improvement (proposed) – Sample 1 Fail, Sample 2 Pass; to be agreed with CO / BCO</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>OI-03</t>
+          <t>OBS-04, 05, 11</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Satisfactory – subject to OI-03</t>
+          <t>Satisfactory – both samples Pass</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>OI-03, OI-06</t>
+          <t>OBS-03, 10, 11</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Satisfactory (preliminary) – subject to OI-03, OI-06</t>
+          <t>Satisfactory – both samples Pass</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -858,22 +858,22 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>0 (pending)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>OI-03, OI-04, OI-05</t>
+          <t>OBS-09, 11 – 16</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Satisfactory (confirm w/ reviewer)</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Pending – OI-04, OI-05 (unable to conclude)</t>
+          <t>Satisfactory – both samples Pass (with observations)</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>OI-03</t>
+          <t>OBS-04, 07, 08, 11</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Satisfactory – subject to OI-03</t>
+          <t>Satisfactory – both samples Pass</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Pass T24 (DEV + UAT); Appian env. pending OI-04</t>
+          <t>Pass (DEV + UAT before go-live; Appian env. screenshots not provided – OBS-16)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Reported as observation OBS-11 (does not affect sample results)</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>C4 CPA cannot be concluded.</t>
+          <t>Both C4 samples concluded Pass on 10/31/2026.</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Reported as observations OBS-14 and OBS-16</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Potential C4 exception (R3 – data disclosure).</t>
+          <t>Control statement does not cover data masking.</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Reported as observations OBS-12 and OBS-13</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4217,12 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>C25 CPA preliminary until confirmed.</t>
+          <t>Approvals were recorded before every deployment; C25 concluded Pass.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Reported as observation OBS-10</t>
         </is>
       </c>
     </row>
@@ -4597,13 +4597,235 @@
       </c>
     </row>
     <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>OBS-11</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Population completeness not re-performed – no independent release list; projects 3512 / 3625 blank SDLC flag (was OI-03).</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>PMO to provide ServiceNow release list with query.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>OBS-12</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Same login MIASANG used on production (miasx1) and non-production (miasx4) (was OI-05).</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Confirm owner and that developers cannot change production.</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>OBS-13</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>T24 MIAAFT28</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Non-production labelled "SANTANDER OCT 2025 EOM" holds client deals – possible production data copy (was OI-05).</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Confirm masking or InfoSec approval.</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>OBS-14</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>No register of development/testing-in-production exceptions and InfoSec approvals (was OI-04).</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Keep a register, even if empty.</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>OBS-15</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Segregated Environments evidence created 10/22/2026 (after period); screenshots undated.</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Capture dated evidence during the period.</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>OBS-16</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>BSI.IT.23.C4</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Appian (SL R01)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>No screenshot of Appian DEV / TEST / PROD environments; relies on ticket test records (was OI-04).</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Provide Appian environment evidence.</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Observation only.</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
